--- a/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Valentine arrive au square avec maman. Maman montre un espace. Maman dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Valentine va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc. Maman voit Valentine. L'adulte voit. Valentine verse le sable frais. Elle fait un gâteau. Un oiseau chante. Valentine reste dans l'espace. Maman dit : je te vois. Valentine sourit. Ses mains sont dans le sable. Plus tard, elle prend le seau. Elle reste encore dans l'espace montré. Maman la voit toujours.</t>
+          <t>Valentine arrive au square avec maman. Maman montre un espace. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Valentine va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc. Maman voit Valentine. L'adulte voit. Valentine verse le sable frais. Elle fait un gâteau. Un oiseau chante. Valentine reste dans l'espace. Je te vois. Valentine sourit. Ses mains sont dans le sable. Plus tard, elle prend le seau. Elle reste encore dans l'espace montré. Maman la voit toujours.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Valentine arrive au square avec maman. Maman montre un espace.
+maman|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
+narrateur|Valentine va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc. Maman voit Valentine. L'adulte voit. Valentine verse le sable frais. Elle fait un gâteau. Un oiseau chante. Valentine reste dans l'espace.
+maman|Je te vois.
+narrateur|Valentine sourit. Ses mains sont dans le sable. Plus tard, elle prend le seau. Elle reste encore dans l'espace montré. Maman la voit toujours.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Valentine joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Valentine est dans l'espace montré. Maman la voit. Le gâteau de sable est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Valentine range le seau. Maman lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Valentine sourit. Ses mains sont dans le sable. Plus tard, elle prend le seau. Elle reste encore dans l'espace montré. Maman la voit toujours.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Valentine joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Valentine est dans l'espace montré. Maman la voit. Le gâteau de sable est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Valentine range le seau. Maman lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Valentine joue où maman voit</t>
+          <t>Le gâteau de sable de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au square, Sarah fait un gâteau de sable dans l'espace que maman a montré. Maman voit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Valentine arrive au square avec maman. Maman montre un espace. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Valentine va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc. Maman voit Valentine. L'adulte voit. Valentine verse le sable frais. Elle fait un gâteau. Un oiseau chante. Valentine reste dans l'espace. Je te vois. Valentine sourit. Ses mains sont dans le sable. Plus tard, elle prend le seau. Elle reste encore dans l'espace montré. Maman la voit toujours.</t>
+          <t>Une feuille jaune colle au banc mouillé. Le square sent le sable encore humide. Un seau rouge est couché dans l'herbe. La gouttière fait plic, tout près. Le bois du banc est froid et lisse. Un moineau picore une miette grise. Sarah marche près de maman. Tu as vu le moineau, Sarah ? Oui, maman. Il picore. En ce moment, Sarah s'approche du bac. Le sable est frais sous les doigts. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Ici, maman ? Oui. Tu restes dans l'espace montré. Sarah va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc mouillé. Maman voit Sarah. L'adulte voit. Sarah verse le sable frais. Le seau rouge est un peu rêche. Je fais un gâteau. Un gâteau de sable ? Oui. Il est tout mou. Sarah appuie avec la paume. Le gâteau sent le sable humide. Un oiseau chante au-dessus du square. Je te vois. L'adulte voit. Tu me vois, maman ? Oui. Tu es dans l'espace montré. Les mains de Sarah restent dans le sable. Elle ajoute une petite feuille jaune. La feuille fait un chapeau tout plat. Un chapeau, maman. Il est joli. Tu joues là où l'adulte a dit. Plus tard, Sarah prend le seau. Elle reste encore dans l'espace montré. Tu restes là où l'adulte a dit ? Oui. Ici. Bravo, Sarah. Tu as fait du bon travail. Maman la voit toujours. La feuille du banc tremble un peu. Le moineau s'envole vers le toit. Il s'envole. Oui. Et toi, tu restes ici. Sarah lisse encore le gâteau. Le sable colle un peu aux genoux. Tu as fini ton gâteau ? Presque. Elle pose le seau à côté. Elle reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Valentine arrive au square avec maman. Maman montre un espace.
-maman|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
-narrateur|Valentine va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc. Maman voit Valentine. L'adulte voit. Valentine verse le sable frais. Elle fait un gâteau. Un oiseau chante. Valentine reste dans l'espace.
+          <t>narrateur|Une feuille jaune colle au banc mouillé.
+narrateur|Le square sent le sable encore humide.
+narrateur|Un seau rouge est couché dans l'herbe.
+narrateur|La gouttière fait plic, tout près.
+narrateur|Le bois du banc est froid et lisse.
+narrateur|Un moineau picore une miette grise.
+narrateur|Sarah marche près de maman.
+maman|Tu as vu le moineau, Sarah ?
+enfant-f|Oui, maman.
+enfant-f|Il picore.
+narrateur|En ce moment, Sarah s'approche du bac.
+narrateur|Le sable est frais sous les doigts.
+maman|Tu joues ici.
+maman|C'est l'espace montré.
+maman|Ici, l'adulte voit.
+enfant-f|Ici, maman ?
+maman|Oui.
+maman|Tu restes dans l'espace montré.
+narrateur|Sarah va au bac à sable.
+narrateur|Elle reste dans l'espace montré.
+narrateur|Maman s'assoit sur le banc mouillé.
+narrateur|Maman voit Sarah.
+narrateur|L'adulte voit.
+narrateur|Sarah verse le sable frais.
+narrateur|Le seau rouge est un peu rêche.
+enfant-f|Je fais un gâteau.
+maman|Un gâteau de sable ?
+enfant-f|Oui.
+enfant-f|Il est tout mou.
+narrateur|Sarah appuie avec la paume.
+narrateur|Le gâteau sent le sable humide.
+narrateur|Un oiseau chante au-dessus du square.
 maman|Je te vois.
-narrateur|Valentine sourit. Ses mains sont dans le sable. Plus tard, elle prend le seau. Elle reste encore dans l'espace montré. Maman la voit toujours.</t>
+maman|L'adulte voit.
+enfant-f|Tu me vois, maman ?
+maman|Oui.
+maman|Tu es dans l'espace montré.
+narrateur|Les mains de Sarah restent dans le sable.
+narrateur|Elle ajoute une petite feuille jaune.
+narrateur|La feuille fait un chapeau tout plat.
+enfant-f|Un chapeau, maman.
+maman|Il est joli.
+maman|Tu joues là où l'adulte a dit.
+narrateur|Plus tard, Sarah prend le seau.
+narrateur|Elle reste encore dans l'espace montré.
+maman|Tu restes là où l'adulte a dit ?
+enfant-f|Oui.
+enfant-f|Ici.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Maman la voit toujours.
+narrateur|La feuille du banc tremble un peu.
+narrateur|Le moineau s'envole vers le toit.
+enfant-f|Il s'envole.
+maman|Oui.
+maman|Et toi, tu restes ici.
+narrateur|Sarah lisse encore le gâteau.
+narrateur|Le sable colle un peu aux genoux.
+maman|Tu as fini ton gâteau ?
+enfant-f|Presque.
+narrateur|Elle pose le seau à côté.
+narrateur|Elle reste dans l'espace montré.
+narrateur|L'adulte voit.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Valentine joue au square. Où joue-t-elle ?</t>
+          <t>Sarah joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Valentine joue au square. Où joue-t-elle ?</t>
+          <t>narrateur|Sarah joue au square.
+narrateur|Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Valentine est dans l'espace montré. Maman la voit. Le gâteau de sable est là.</t>
+          <t>Sarah est dans l'espace montré. Maman la voit. L'adulte voit. Le gâteau de sable est là. Tu as joué dans l'espace montré ? Oui. Bravo. L'adulte voit. Le seau rouge brille un peu. La petite feuille reste sur le gâteau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1743,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Valentine est dans l'espace montré. Maman la voit. Le gâteau de sable est là.</t>
+          <t>narrateur|Sarah est dans l'espace montré.
+narrateur|Maman la voit.
+narrateur|L'adulte voit.
+narrateur|Le gâteau de sable est là.
+maman|Tu as joué dans l'espace montré ?
+enfant-f|Oui.
+maman|Bravo.
+maman|L'adulte voit.
+narrateur|Le seau rouge brille un peu.
+narrateur|La petite feuille reste sur le gâteau.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Valentine range le seau. Maman lui tend la main.</t>
+          <t>Sarah range le seau. Le sable tombe, tout doux. Tu as fini de ranger ? Oui, maman. Bravo. Donne-moi la main. Maman lui tend la main. La feuille jaune reste sur le banc. Le square sent encore le sable mouillé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1920,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Valentine range le seau. Maman lui tend la main.</t>
+          <t>narrateur|Sarah range le seau.
+narrateur|Le sable tombe, tout doux.
+maman|Tu as fini de ranger ?
+enfant-f|Oui, maman.
+maman|Bravo.
+maman|Donne-moi la main.
+narrateur|Maman lui tend la main.
+narrateur|La feuille jaune reste sur le banc.
+narrateur|Le square sent encore le sable mouillé.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah tient la main de maman. On a fait un gâteau. Oui. Dans l'espace montré. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2096,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Sarah tient la main de maman.
+enfant-f|On a fait un gâteau.
+maman|Oui.
+maman|Dans l'espace montré.
+maman|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille jaune colle au banc mouillé. Le square sent le sable encore humide. Un seau rouge est couché dans l'herbe. La gouttière fait plic, tout près. Le bois du banc est froid et lisse. Un moineau picore une miette grise. Sarah marche près de maman. Tu as vu le moineau, Sarah ? Oui, maman. Il picore. En ce moment, Sarah s'approche du bac. Le sable est frais sous les doigts. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Ici, maman ? Oui. Tu restes dans l'espace montré. Sarah va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc mouillé. Maman voit Sarah. L'adulte voit. Sarah verse le sable frais. Le seau rouge est un peu rêche. Je fais un gâteau. Un gâteau de sable ? Oui. Il est tout mou. Sarah appuie avec la paume. Le gâteau sent le sable humide. Un oiseau chante au-dessus du square. Je te vois. L'adulte voit. Tu me vois, maman ? Oui. Tu es dans l'espace montré. Les mains de Sarah restent dans le sable. Elle ajoute une petite feuille jaune. La feuille fait un chapeau tout plat. Un chapeau, maman. Il est joli. Tu joues là où l'adulte a dit. Plus tard, Sarah prend le seau. Elle reste encore dans l'espace montré. Tu restes là où l'adulte a dit ? Oui. Ici. Bravo, Sarah. Tu as fait du bon travail. Maman la voit toujours. La feuille du banc tremble un peu. Le moineau s'envole vers le toit. Il s'envole. Oui. Et toi, tu restes ici. Sarah lisse encore le gâteau. Le sable colle un peu aux genoux. Tu as fini ton gâteau ? Presque. Elle pose le seau à côté. Elle reste dans l'espace montré. L'adulte voit.</t>
+          <t>Une feuille jaune colle au banc mouillé. Le square sent le sable encore humide. Un seau rouge est couché dans l'herbe. La gouttière fait plic, tout près. Le bois du banc est froid et lisse. Un moineau picore une miette grise. Sarah marche près de maman. Tu as vu le moineau, Sarah ? Oui, maman. Il picore. En ce moment, Sarah s'approche du bac. Le sable est frais sous les doigts. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Ici, maman ? Oui. Tu restes dans l'espace montré. Sarah va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc mouillé. Maman voit Sarah. L'adulte voit. Sarah verse le sable frais. Le seau rouge est un peu rêche. Je fais un gâteau. Un gâteau de sable ? Oui. Il est tout mou. Sarah appuie avec la paume. Le gâteau sent le sable humide. Un oiseau chante au-dessus du square. Je te vois. L'adulte voit. Tu me vois, maman ? Oui. Tu es dans l'espace montré. Les mains de Sarah restent dans le sable. Elle ajoute une petite feuille jaune. La feuille fait un chapeau tout plat. Un chapeau, maman. Il est joli. Tu joues là où l'adulte a dit. Plus tard, Sarah prend le seau. Elle reste encore dans l'espace montré. Tu restes là où l'adulte a dit ? Oui. Ici. Bravo, Sarah. Maman la voit toujours. La feuille du banc tremble un peu. Le moineau s'envole vers le toit. Il s'envole. Oui. Et toi, tu restes ici. Sarah lisse encore le gâteau. Le sable colle un peu aux genoux. Tu as fini ton gâteau ? Presque. Elle pose le seau à côté. Elle reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Valentine arrive au square avec maman. Maman montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. Maman dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Valentine va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc. Maman voit Valentine. L'adulte voit. Valentine verse le sable frais. Elle fait un gâteau. Un oiseau chante. Valentine reste dans l'espace. Maman dit : je te vois. Valentine sourit. Ses mains sont dans le sable. Plus tard, elle prend le seau. Elle reste encore dans l'espace montré. Maman la voit toujours.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille jaune colle au banc mouillé. Le square sent le sable encore humide. Un seau rouge est couché dans l'herbe. La gouttière fait plic, tout près. Le bois du banc est froid et lisse. Un moineau picore une miette grise. Sarah marche près de maman. Tu as vu le moineau, Sarah ? Oui, maman. Il picore. En ce moment, Sarah s'approche du bac. Le sable est frais sous les doigts. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Ici, maman ? Oui. Tu restes dans l'espace montré. Sarah va au bac à sable. Elle reste dans l'espace montré. Maman s'assoit sur le banc mouillé. Maman voit Sarah. L'adulte voit. Sarah verse le sable frais. Le seau rouge est un peu rêche. Je fais un gâteau. Un gâteau de sable ? Oui. Il est tout mou. Sarah appuie avec la paume. Le gâteau sent le sable humide. Un oiseau chante au-dessus du square. Je te vois. L'adulte voit. Tu me vois, maman ? Oui. Tu es dans l'espace montré. Les mains de Sarah restent dans le sable. Elle ajoute une petite feuille jaune. La feuille fait un chapeau tout plat. Un chapeau, maman. Il est joli. Tu joues là où l'adulte a dit. Plus tard, Sarah prend le seau. Elle reste encore dans l'espace montré. Tu restes là où l'adulte a dit ? Oui. Ici. Bravo, Sarah. Maman la voit toujours. La feuille du banc tremble un peu. Le moineau s'envole vers le toit. Il s'envole. Oui. Et toi, tu restes ici. Sarah lisse encore le gâteau. Le sable colle un peu aux genoux. Tu as fini ton gâteau ? Presque. Elle pose le seau à côté. Elle reste dans l'espace montré. L'adulte voit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 enfant-f|Oui.
 enfant-f|Ici.
 maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
 narrateur|Maman la voit toujours.
 narrateur|La feuille du banc tremble un peu.
 narrateur|Le moineau s'envole vers le toit.
@@ -1389,7 +1388,6 @@
 narrateur|L'adulte voit.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1419,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Valentine joue au square. Où joue-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1572,6 @@
 narrateur|Où joue-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1604,7 +1601,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Valentine est dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Maman la voit. Le gâteau de sable est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est dans l'espace montré. Maman la voit. L'adulte voit. Le gâteau de sable est là. Tu as joué dans l'espace montré ? Oui. Bravo. L'adulte voit. Le seau rouge brille un peu. La petite feuille reste sur le gâteau.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,7 +1752,6 @@
 narrateur|La petite feuille reste sur le gâteau.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Valentine range le seau. Maman lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range le seau. Le sable tombe, tout doux. Tu as fini de ranger ? Oui, maman. Bravo. Donne-moi la main. Maman lui tend la main. La feuille jaune reste sur le banc. Le square sent encore le sable mouillé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,7 +1927,6 @@
 narrateur|Le square sent encore le sable mouillé.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Sarah tient la main de maman. On a fait un gâteau. Oui. Dans l'espace montré. Bravo, Sarah. L'histoire est finie.</t>
+          <t>Sarah tient la main de maman. On a fait un gâteau. Oui. Dans l'espace montré. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah tient la main de maman. On a fait un gâteau. Oui. Dans l'espace montré. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,11 +2095,9 @@
 enfant-f|On a fait un gâteau.
 maman|Oui.
 maman|Dans l'espace montré.
-maman|Bravo, Sarah.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Sarah.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>square, bac à sable</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Valentine, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
